--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N51_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N51_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.62090119257045</v>
+        <v>4.975896443792699</v>
       </c>
       <c r="D2" t="n">
-        <v>30.65609170236185</v>
+        <v>4.9816149016338</v>
       </c>
       <c r="E2" t="n">
-        <v>5.272873698333297</v>
+        <v>0.8568419759791608</v>
       </c>
       <c r="F2" t="n">
-        <v>5.312212018189372</v>
+        <v>0.8632344529557731</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.57696427900365</v>
+        <v>5.293756695338093</v>
       </c>
       <c r="D3" t="n">
-        <v>32.65369066348444</v>
+        <v>5.306224732816221</v>
       </c>
       <c r="E3" t="n">
-        <v>5.272873698333297</v>
+        <v>0.8568419759791608</v>
       </c>
       <c r="F3" t="n">
-        <v>5.312212018189372</v>
+        <v>0.8632344529557731</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.03493582548539</v>
+        <v>3.255677071641375</v>
       </c>
       <c r="D4" t="n">
-        <v>20.05150327638266</v>
+        <v>3.258369282412183</v>
       </c>
       <c r="E4" t="n">
-        <v>5.272873698333297</v>
+        <v>0.8568419759791608</v>
       </c>
       <c r="F4" t="n">
-        <v>5.312212018189372</v>
+        <v>0.8632344529557731</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.05776878738575</v>
+        <v>5.371887427950184</v>
       </c>
       <c r="D5" t="n">
-        <v>33.13009584082698</v>
+        <v>5.383640574134385</v>
       </c>
       <c r="E5" t="n">
-        <v>5.272873698333297</v>
+        <v>0.8568419759791608</v>
       </c>
       <c r="F5" t="n">
-        <v>5.312212018189372</v>
+        <v>0.8632344529557731</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.28718277036795</v>
+        <v>3.784167200184792</v>
       </c>
       <c r="D6" t="n">
-        <v>23.21385157810151</v>
+        <v>3.772250881441495</v>
       </c>
       <c r="E6" t="n">
-        <v>5.272873698333297</v>
+        <v>0.8568419759791608</v>
       </c>
       <c r="F6" t="n">
-        <v>5.312212018189372</v>
+        <v>0.8632344529557731</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
